--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_67_R7.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_67_R7.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7812</v>
+        <v>5.7461</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1802</v>
+        <v>3.4475</v>
       </c>
       <c r="F2" t="n">
-        <v>2.601</v>
+        <v>2.2986</v>
       </c>
       <c r="G2" t="n">
         <v>1.3519</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>1.017</v>
+        <v>0.9818</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4525</v>
+        <v>0.7198</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5645</v>
+        <v>0.2621</v>
       </c>
       <c r="V2" t="n">
         <v>1.3247</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7042</v>
+        <v>3.0416</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9602</v>
+        <v>3.432</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.256</v>
+        <v>-0.3905</v>
       </c>
       <c r="G3" t="n">
         <v>2.9001</v>
@@ -688,13 +688,13 @@
         <v>0.232</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4279</v>
+        <v>-0.0905</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5228</v>
+        <v>-0.051</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0949</v>
+        <v>-0.0395</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6631</v>
+        <v>2.7445</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8381</v>
+        <v>0.7516</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8249</v>
+        <v>1.993</v>
       </c>
       <c r="G4" t="n">
         <v>0.2075</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9221</v>
+        <v>1.0036</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1483</v>
+        <v>1.0618</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2262</v>
+        <v>-0.0582</v>
       </c>
       <c r="V4" t="n">
         <v>0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6052</v>
+        <v>1.4275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0279</v>
+        <v>-0.0154</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5773</v>
+        <v>1.4429</v>
       </c>
       <c r="G5" t="n">
         <v>2.391</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9796</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4446</v>
+        <v>0.4013</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5351</v>
+        <v>0.4007</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1839</v>
+        <v>1.3355</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0125</v>
+        <v>0.1305</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1714</v>
+        <v>1.205</v>
       </c>
       <c r="G6" t="n">
         <v>0.0764</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0523</v>
+        <v>0.0993</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.9749</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0583</v>
+        <v>1.5529</v>
       </c>
       <c r="F7" t="n">
-        <v>0.551</v>
+        <v>-0.578</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1392</v>
+        <v>-2.0493</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1392</v>
+        <v>-2.1631</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.1138</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0504</v>
+        <v>-1.6524</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0504</v>
+        <v>-2.191</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.5386</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1896</v>
+        <v>-0.3969</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1896</v>
+        <v>0.0279</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.4248</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0527</v>
+        <v>-0.1898</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.1531</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0448</v>
+        <v>-0.0367</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.3584</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5203</v>
+        <v>0.6766</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1991</v>
+        <v>0.0583</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6788</v>
+        <v>0.6183</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0493</v>
+        <v>-0.1392</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1631</v>
+        <v>-0.1392</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1138</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6524</v>
+        <v>0.0504</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.191</v>
+        <v>0.0504</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5386</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3969</v>
+        <v>-0.1896</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0279</v>
+        <v>-0.1896</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4248</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6445</v>
+        <v>0.1199</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.507</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1375</v>
+        <v>0.112</v>
       </c>
       <c r="V8" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2645</v>
+        <v>0.0696</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7783</v>
+        <v>-1.9395</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0427</v>
+        <v>2.0091</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1182</v>
@@ -1156,13 +1156,13 @@
         <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3104</v>
+        <v>1.1156</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2977</v>
+        <v>1.1365</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0127</v>
+        <v>-0.0209</v>
       </c>
       <c r="V9" t="n">
         <v>1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1388</v>
+        <v>-0.2076</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6119</v>
+        <v>-1.891</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7506</v>
+        <v>1.6834</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5047</v>
@@ -1234,13 +1234,13 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9656</v>
+        <v>0.6192</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8417</v>
+        <v>0.5625</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1239</v>
+        <v>0.0567</v>
       </c>
       <c r="V10" t="n">
         <v>0.1418</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1734</v>
+        <v>-0.4319</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3545</v>
+        <v>0.131</v>
       </c>
       <c r="F11" t="n">
-        <v>0.181</v>
+        <v>-0.5629</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1542</v>
+        <v>0.4902</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1069</v>
+        <v>0.8681</v>
       </c>
       <c r="I11" t="n">
-        <v>0.261</v>
+        <v>-0.378</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2318</v>
+        <v>1.7701</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2318</v>
+        <v>1.5124</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.2576</v>
       </c>
       <c r="M11" t="n">
-        <v>0.386</v>
+        <v>-1.2799</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1249</v>
+        <v>-0.6443</v>
       </c>
       <c r="O11" t="n">
-        <v>0.261</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6959</v>
+        <v>2.5515</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4378</v>
+        <v>0.06</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1246</v>
+        <v>0.6805</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3132</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>-1.214</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7014</v>
+        <v>-0.6982</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1049</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5965</v>
+        <v>0.2147</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4902</v>
+        <v>0.1542</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8681</v>
+        <v>-0.1069</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.378</v>
+        <v>0.261</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7701</v>
+        <v>-0.2318</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5124</v>
+        <v>-0.2318</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2576</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2799</v>
+        <v>0.386</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6443</v>
+        <v>0.1249</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.261</v>
       </c>
       <c r="P12" t="n">
-        <v>0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2095</v>
+        <v>0.9131</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4446</v>
+        <v>0.5663</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6541</v>
+        <v>0.3468</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X12" t="n">
         <v>-1.214</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4489</v>
+        <v>-0.7851</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5373</v>
+        <v>-0.1087</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9116</v>
+        <v>-0.6763</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8119</v>
@@ -1468,13 +1468,13 @@
         <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0855</v>
+        <v>-0.4217</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6642</v>
+        <v>-0.2357</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4213</v>
+        <v>-0.186</v>
       </c>
       <c r="V13" t="n">
         <v>2.1444</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.1469</v>
+        <v>13.8935</v>
       </c>
       <c r="E14" t="n">
-        <v>3.889399999999999</v>
+        <v>4.636400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>9.256999999999998</v>
+        <v>9.257300000000003</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9479999999999995</v>
+        <v>0.9480000000000004</v>
       </c>
       <c r="H14" t="n">
         <v>4.093299999999999</v>
@@ -1531,7 +1531,7 @@
         <v>-4.4861</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2379000000000001</v>
+        <v>-0.2379</v>
       </c>
       <c r="O14" t="n">
         <v>-4.2481</v>
@@ -1546,13 +1546,13 @@
         <v>17.3966</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2655</v>
+        <v>5.012399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9932</v>
+        <v>4.740100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2723999999999999</v>
+        <v>0.2724999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>5.6135</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5332</v>
+        <v>4.2244</v>
       </c>
       <c r="E15" t="n">
-        <v>4.375</v>
+        <v>4.7289</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8418</v>
+        <v>-0.5044</v>
       </c>
       <c r="G15" t="n">
         <v>4.0923</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0518</v>
+        <v>0.7431</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1687</v>
+        <v>0.1852</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2205</v>
+        <v>0.5579</v>
       </c>
       <c r="V15" t="n">
         <v>-2.0026</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4509</v>
+        <v>3.9734</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5617</v>
+        <v>1.6796</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8892</v>
+        <v>2.2938</v>
       </c>
       <c r="G16" t="n">
         <v>2.7693</v>
@@ -1702,13 +1702,13 @@
         <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5324</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0272</v>
+        <v>0.0907</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5052</v>
+        <v>-0.1006</v>
       </c>
       <c r="V16" t="n">
         <v>1.214</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3436</v>
+        <v>0.5681</v>
       </c>
       <c r="E17" t="n">
         <v>0.0672</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2764</v>
+        <v>0.5008</v>
       </c>
       <c r="G17" t="n">
         <v>0.1494</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2697</v>
+        <v>-0.0452</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2697</v>
+        <v>-0.0452</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.238</v>
+        <v>0.211</v>
       </c>
       <c r="E18" t="n">
         <v>0.8101</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0481</v>
+        <v>-0.5991</v>
       </c>
       <c r="G18" t="n">
         <v>3.1205</v>
@@ -1858,13 +1858,13 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8224</v>
+        <v>-0.3734</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2592</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5632</v>
+        <v>-0.1142</v>
       </c>
       <c r="V18" t="n">
         <v>-1.6083</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4255</v>
+        <v>-0.0463</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9311</v>
+        <v>-0.4713</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0354</v>
@@ -1936,13 +1936,13 @@
         <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.148</v>
+        <v>-0.1601</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9085</v>
+        <v>0.4367</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0565</v>
+        <v>-0.5968</v>
       </c>
       <c r="V19" t="n">
         <v>0.1418</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8834</v>
+        <v>-0.9233</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0153</v>
+        <v>0.4256</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8987</v>
+        <v>-1.3489</v>
       </c>
       <c r="G20" t="n">
         <v>0.9979</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2631</v>
+        <v>0.2232</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7591</v>
+        <v>0.1693</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.496</v>
+        <v>0.0538</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1444</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8964</v>
+        <v>-1.0309</v>
       </c>
       <c r="E21" t="n">
         <v>-0.7906</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1058</v>
+        <v>-0.2402</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9483</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0518</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1265</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1292</v>
+        <v>-1.7018</v>
       </c>
       <c r="E22" t="n">
         <v>-2.7899</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6607</v>
+        <v>1.0881</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5923</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0009</v>
+        <v>0.4266</v>
       </c>
       <c r="T22" t="n">
         <v>0.0553</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0562</v>
+        <v>0.3712</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4214</v>
+        <v>-2.5793</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4741</v>
+        <v>-3.6225</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9473</v>
+        <v>1.0432</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4119</v>
+        <v>-3.2644</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5052</v>
+        <v>-1.9795</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9067</v>
+        <v>-1.2849</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0606</v>
+        <v>-3.0567</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4214</v>
+        <v>-1.1995</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6391</v>
+        <v>-1.8572</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3513</v>
+        <v>-0.2077</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0838</v>
+        <v>-0.78</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2676</v>
+        <v>0.5723</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1502</v>
+        <v>-0.2427</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8338</v>
+        <v>-0.5658</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6835</v>
+        <v>0.3231</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.802</v>
+        <v>-3.3302</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8482</v>
+        <v>-2.3764</v>
       </c>
       <c r="F24" t="n">
         <v>-0.9538</v>
@@ -2326,10 +2326,10 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8531</v>
+        <v>-0.3813</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7468</v>
+        <v>-0.275</v>
       </c>
       <c r="U24" t="n">
         <v>-0.1063</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8711</v>
+        <v>-3.9883</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0943</v>
+        <v>-3.0639</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2233</v>
+        <v>-0.9245</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.2644</v>
+        <v>-3.4119</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.9795</v>
+        <v>-2.5052</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2849</v>
+        <v>-0.9067</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.0567</v>
+        <v>-2.0606</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1995</v>
+        <v>-1.4214</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.8572</v>
+        <v>-0.6391</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2077</v>
+        <v>-1.3513</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.78</v>
+        <v>-1.0838</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5723</v>
+        <v>-0.2676</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5345</v>
+        <v>-0.4167</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0376</v>
+        <v>0.244</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4968</v>
+        <v>-0.6607</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.7273</v>
+        <v>-4.1204</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.5148</v>
+        <v>-4.2789</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2125</v>
+        <v>0.1585</v>
       </c>
       <c r="G26" t="n">
         <v>-1.8737</v>
@@ -2482,13 +2482,13 @@
         <v>1.1598</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6216</v>
+        <v>-0.0147</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5149</v>
+        <v>-0.279</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1067</v>
+        <v>0.2642</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0722</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-13.1466</v>
+        <v>-9.2149</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.257099999999998</v>
+        <v>-9.257099999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.8895</v>
+        <v>0.04220000000000004</v>
       </c>
       <c r="G27" t="n">
         <v>-0.9481000000000006</v>
@@ -2533,10 +2533,10 @@
         <v>3.1453</v>
       </c>
       <c r="J27" t="n">
-        <v>4.4861</v>
+        <v>4.486100000000002</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2377999999999998</v>
+        <v>0.2378</v>
       </c>
       <c r="L27" t="n">
         <v>4.2483</v>
@@ -2560,13 +2560,13 @@
         <v>15.0769</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.2657</v>
+        <v>-0.3337</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2724000000000001</v>
+        <v>-0.2725</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.9931</v>
+        <v>-0.06150000000000011</v>
       </c>
       <c r="V27" t="n">
         <v>-5.6135</v>
